--- a/data/trending_integrated_20261021_10.xlsx
+++ b/data/trending_integrated_20261021_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10400</v>
+        <v>10680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+6.45%</t>
+          <t>'+9.31%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
         <v>1.28</v>
@@ -610,7 +610,7 @@
         <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>105280145425</v>
+        <v>111758574510</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HT로보틱스 신고가 돌파 기대감과 함께 로봇주 섹터 강세. 7천억 수주 잔고 근거.</t>
+          <t>로봇주 섹터 상승 속 HT로보틱스 신고가 기대감. 고점 급락 우려와 함께 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', '수주잔고']</t>
+          <t>['로봇주', '신고가', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="G3" t="n">
-        <v>1417</v>
+        <v>1353</v>
       </c>
       <c r="H3" t="n">
         <v>48.77</v>
@@ -702,7 +702,7 @@
         <v>48.81</v>
       </c>
       <c r="O3" t="n">
-        <v>1667964567000</v>
+        <v>1820719446500</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 우려에도 불구하고 차트상 V자 반등 및 150만 전자 돌파 기대감.</t>
+          <t>솔리다임 상장 여부가 SK하이닉스 주가에 영향. V자 반등 및 목표가 제시, 개미 투자자 주의 당부.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '솔리다임', '차트']</t>
+          <t>['솔리다임', '반도체 수출', 'V자 반등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G4" t="n">
-        <v>1913</v>
+        <v>1640</v>
       </c>
       <c r="H4" t="n">
         <v>46.08</v>
@@ -794,7 +794,7 @@
         <v>46.04</v>
       </c>
       <c r="O4" t="n">
-        <v>1051160601000</v>
+        <v>1141826549250</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국/중국 반도체 갈등 및 슈퍼마이크로 실적 호조에 따른 급등 기대감. 외인 매수세 유입 및 공매도 폐지 논의.</t>
+          <t>미국 반도체 산업 호재 및 외국인 매수세 유입에 따른 삼성전자 급등 전망. 공매도 폐지 요구.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '공매도']</t>
+          <t>['반도체', '외국인 매수', '급등 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14460</v>
+        <v>1612</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.12%</t>
+          <t>'+2.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.04</v>
+        <v>-0.93</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H5" t="n">
-        <v>9.82</v>
+        <v>0.84</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14160</v>
+        <v>1573</v>
       </c>
       <c r="K5" t="n">
-        <v>14340</v>
+        <v>1650</v>
       </c>
       <c r="L5" t="n">
-        <v>14780</v>
+        <v>1715</v>
       </c>
       <c r="M5" t="n">
-        <v>14340</v>
+        <v>1573</v>
       </c>
       <c r="N5" t="n">
-        <v>9.779999999999999</v>
+        <v>1.77</v>
       </c>
       <c r="O5" t="n">
-        <v>10968419480</v>
+        <v>23409934342</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>2970</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>890</v>
       </c>
       <c r="R5" t="n">
-        <v>77000</v>
+        <v>-553000</v>
       </c>
       <c r="S5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인/연기금 매수세에도 불구하고 종가 음봉 및 실적 기대감 하락. 주가 조작 의혹 제기.</t>
+          <t>스페이스X 관련 기대감 속 일부 긍정적 신호와 프로그램 매도 상존. 텐버거 기대감 나타나나 단기 차익 실현 권고.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적주', '주가조작', '공매도']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2865</v>
+        <v>14440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'+1.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="H6" t="n">
-        <v>5.82</v>
+        <v>9.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2840</v>
+        <v>14160</v>
       </c>
       <c r="K6" t="n">
-        <v>3100</v>
+        <v>14340</v>
       </c>
       <c r="L6" t="n">
-        <v>3300</v>
+        <v>14780</v>
       </c>
       <c r="M6" t="n">
-        <v>2860</v>
+        <v>14340</v>
       </c>
       <c r="N6" t="n">
-        <v>5.91</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>14092566119</v>
+        <v>12027165780</v>
       </c>
       <c r="P6" t="n">
-        <v>19950</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>1913</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-1054000</v>
+        <v>77000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 투자 기업 실적 호조 및 합병 언급으로 인한 상승 기대. 불공정 거래 신고 독려.</t>
+          <t>외국인, 연기금 프로그램 매수세에도 주가 상승 둔화. 실적주 기대감 있으나 하락 우려와 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '합병', '불공정거래']</t>
+          <t>['외국인 매수', '실적주', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63000</v>
+        <v>2880</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>241</v>
+        <v>115</v>
       </c>
       <c r="H7" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K7" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L7" t="n">
-        <v>64300</v>
+        <v>3300</v>
       </c>
       <c r="M7" t="n">
-        <v>62600</v>
+        <v>2855</v>
       </c>
       <c r="N7" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O7" t="n">
-        <v>31334606750</v>
+        <v>14429735584</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R7" t="n">
-        <v>-26000</v>
+        <v>-1054000</v>
       </c>
       <c r="S7" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SMR 관련 기대감에도 불구하고 외인 매도세 및 지수 대비 낮은 상승률. 주가 누르기 방지법 청원.</t>
+          <t>스페이스X 관련 투자 언급에도 주가 지지부진. 외인 갭 띄우고 팔기, 주가 조작 의혹 제기. 합병 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SMR', '외인매도', '공매도']</t>
+          <t>['스페이스X', '주가 조작', '합병']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17350</v>
+        <v>63100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.17%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="H8" t="n">
-        <v>27.78</v>
+        <v>22.23</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17320</v>
+        <v>62800</v>
       </c>
       <c r="K8" t="n">
-        <v>17480</v>
+        <v>63600</v>
       </c>
       <c r="L8" t="n">
-        <v>17820</v>
+        <v>64300</v>
       </c>
       <c r="M8" t="n">
-        <v>17320</v>
+        <v>62600</v>
       </c>
       <c r="N8" t="n">
-        <v>27.78</v>
+        <v>22.29</v>
       </c>
       <c r="O8" t="n">
-        <v>13610407620</v>
+        <v>34255544050</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>106000</v>
+        <v>-26000</v>
       </c>
       <c r="S8" t="n">
-        <v>33000</v>
+        <v>-23000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 조선업 부진으로 인한 급락 전망. 반도체 섹터로의 이동 촉구.</t>
+          <t>SMR 사업 관련 기대감에도 불구하고, 개인 투자자들은 시장 소외 및 정부 정책 부재에 대한 불만을 표출하며 주가 상승 동력 상실을 우려하고 있다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['조선업', '반도체', '급락']</t>
+          <t>['SMR', '개미', '외인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4265</v>
+        <v>7280</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="H9" t="n">
-        <v>8.58</v>
+        <v>25.45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,58 +1239,334 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4630</v>
+        <v>7270</v>
       </c>
       <c r="K9" t="n">
-        <v>4645</v>
+        <v>7360</v>
       </c>
       <c r="L9" t="n">
-        <v>4645</v>
+        <v>7420</v>
       </c>
       <c r="M9" t="n">
-        <v>4265</v>
+        <v>7250</v>
       </c>
       <c r="N9" t="n">
-        <v>8.57</v>
+        <v>25.4</v>
       </c>
       <c r="O9" t="n">
-        <v>12818977998</v>
+        <v>4433162365</v>
       </c>
       <c r="P9" t="n">
-        <v>7560</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>2930</v>
+        <v>7190</v>
       </c>
       <c r="R9" t="n">
-        <v>-638000</v>
+        <v>39000</v>
       </c>
       <c r="S9" t="n">
-        <v>-25000</v>
+        <v>-5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>프로그램 매도세 강세 및 주가 누르기 의혹 제기. 증권사 리포트 부정적 평가.</t>
+          <t>외인 비중 높은 종목이나 개인 매수세만으로는 상승력 부족. 업종 변경 및 주가 관리 부실 지적, 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['외인 비중', '주가 관리', '개인 매수']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17260</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-0.35%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>139</v>
+      </c>
+      <c r="H10" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>17320</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17480</v>
+      </c>
+      <c r="L10" t="n">
+        <v>17820</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17170</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16053907045</v>
+      </c>
+      <c r="P10" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17170</v>
+      </c>
+      <c r="R10" t="n">
+        <v>106000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>33000</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>조선업 섹터 부진 속 삼성중공업 주가 하락. 반도체 섹터로 자금 이동, 외인 매수세 유입에도 종목 자체 부진.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['조선업', '주가 하락', '반도체 섹터']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3075</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-4.95%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="E11" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G11" t="n">
+        <v>128</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3235</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3170</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3035</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6380035922</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>김정은 사망설 관련주로 급락. 출처 불분명한 이슈에 따른 변동성 확대, 공매도 세력과의 갈등.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['프로그램매도', '주가조작', '공매도']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['김정은 사망설', '급락', '공매도']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4265</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-7.88%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>258</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>4630</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4645</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4645</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4240</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14434286670</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7560</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2930</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-638000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>프로그램 매도세 강하며 주가 하락 지속. 공매도 및 누르기 의혹 제기, 경영진 비판.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['프로그램 매도', '공매도', '주가 누르기']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>088350</t>
         </is>

--- a/data/trending_integrated_20261021_10.xlsx
+++ b/data/trending_integrated_20261021_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10680</v>
+        <v>10740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+9.31%</t>
+          <t>'+9.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H2" t="n">
         <v>1.28</v>
@@ -610,7 +610,7 @@
         <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>111758574510</v>
+        <v>119499549245</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1292000</v>
+        <v>9340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.64%</t>
+          <t>'+7.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>523</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>1353</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>48.77</v>
+        <v>5.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1223000</v>
+        <v>8650</v>
       </c>
       <c r="K3" t="n">
-        <v>1260000</v>
+        <v>9010</v>
       </c>
       <c r="L3" t="n">
-        <v>1319000</v>
+        <v>9380</v>
       </c>
       <c r="M3" t="n">
-        <v>1258000</v>
+        <v>8790</v>
       </c>
       <c r="N3" t="n">
-        <v>48.81</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>1820719446500</v>
+        <v>10230097735</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q3" t="n">
-        <v>468000</v>
+        <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>45000</v>
+        <v>-42000</v>
       </c>
       <c r="S3" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>솔리다임 상장 여부가 SK하이닉스 주가에 영향. V자 반등 및 목표가 제시, 개미 투자자 주의 당부.</t>
+          <t>자회사 나스닥 상장 철회 소식. 중복상장 금지 이슈와 테슬라 관련주로서의 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['솔리다임', '반도체 수출', 'V자 반등']</t>
+          <t>['나스닥', '중복상장', '테슬라']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221250</v>
+        <v>1298000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+6.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="G4" t="n">
-        <v>1640</v>
+        <v>1374</v>
       </c>
       <c r="H4" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>211500</v>
+        <v>1223000</v>
       </c>
       <c r="K4" t="n">
-        <v>217000</v>
+        <v>1260000</v>
       </c>
       <c r="L4" t="n">
-        <v>224750</v>
+        <v>1319000</v>
       </c>
       <c r="M4" t="n">
-        <v>217000</v>
+        <v>1258000</v>
       </c>
       <c r="N4" t="n">
-        <v>46.04</v>
+        <v>48.81</v>
       </c>
       <c r="O4" t="n">
-        <v>1141826549250</v>
+        <v>1935470610500</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R4" t="n">
-        <v>446000</v>
+        <v>45000</v>
       </c>
       <c r="S4" t="n">
-        <v>262000</v>
+        <v>56000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 반도체 산업 호재 및 외국인 매수세 유입에 따른 삼성전자 급등 전망. 공매도 폐지 요구.</t>
+          <t>솔리다임 상장 관련 이슈 및 V자 반등 기대감. 국내외 반도체 시장 상황 및 투자자 심리 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '외국인 매수', '급등 전망']</t>
+          <t>['솔리다임', '반도체', 'V자 반등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1612</v>
+        <v>222250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.48%</t>
+          <t>'+5.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.93</v>
+        <v>0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>504</v>
       </c>
       <c r="G5" t="n">
-        <v>113</v>
+        <v>1448</v>
       </c>
       <c r="H5" t="n">
-        <v>0.84</v>
+        <v>46.08</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1573</v>
+        <v>211500</v>
       </c>
       <c r="K5" t="n">
-        <v>1650</v>
+        <v>217000</v>
       </c>
       <c r="L5" t="n">
-        <v>1715</v>
+        <v>224750</v>
       </c>
       <c r="M5" t="n">
-        <v>1573</v>
+        <v>217000</v>
       </c>
       <c r="N5" t="n">
-        <v>1.77</v>
+        <v>46.04</v>
       </c>
       <c r="O5" t="n">
-        <v>23409934342</v>
+        <v>1217249215500</v>
       </c>
       <c r="P5" t="n">
-        <v>2970</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>890</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>-553000</v>
+        <v>446000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>262000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 관련 기대감 속 일부 긍정적 신호와 프로그램 매도 상존. 텐버거 기대감 나타나나 단기 차익 실현 권고.</t>
+          <t>미국-중국 반도체 갈등 속 외국인 순매수 지속. 공매도 폐지 요구 및 반도체 판매 증가 추세.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['반도체', '외국인', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14440</v>
+        <v>14540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.98%</t>
+          <t>'+2.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H6" t="n">
         <v>9.82</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>12027165780</v>
+        <v>12781207500</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인, 연기금 프로그램 매수세에도 주가 상승 둔화. 실적주 기대감 있으나 하락 우려와 주가 조작 의혹 제기.</t>
+          <t>주가 누르기 및 공매도 관련 불만 제기. 외국인, 연기금 매수세 유입 및 실적 개선 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 매수', '실적주', '주가 조작']</t>
+          <t>['공매도', '누르기', '실적주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2880</v>
+        <v>1608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.09</v>
+        <v>-0.93</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="H7" t="n">
-        <v>5.82</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2840</v>
+        <v>1573</v>
       </c>
       <c r="K7" t="n">
-        <v>3100</v>
+        <v>1650</v>
       </c>
       <c r="L7" t="n">
-        <v>3300</v>
+        <v>1715</v>
       </c>
       <c r="M7" t="n">
-        <v>2855</v>
+        <v>1573</v>
       </c>
       <c r="N7" t="n">
-        <v>5.91</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>14429735584</v>
+        <v>24406397273</v>
       </c>
       <c r="P7" t="n">
-        <v>19950</v>
+        <v>2970</v>
       </c>
       <c r="Q7" t="n">
-        <v>1913</v>
+        <v>890</v>
       </c>
       <c r="R7" t="n">
-        <v>-1054000</v>
+        <v>-553000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>스페이스X 관련 투자 언급에도 주가 지지부진. 외인 갭 띄우고 팔기, 주가 조작 의혹 제기. 합병 관련 언급.</t>
+          <t>스페이스X 관련주 부각 및 주가 상승 기대. 다만, 개인 투자자 매수세와 프로그램 매도세 관찰 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['스페이스X', '주가 조작', '합병']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63100</v>
+        <v>2900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+2.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="H8" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K8" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L8" t="n">
-        <v>64300</v>
+        <v>3300</v>
       </c>
       <c r="M8" t="n">
-        <v>62600</v>
+        <v>2855</v>
       </c>
       <c r="N8" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O8" t="n">
-        <v>34255544050</v>
+        <v>14618787944</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R8" t="n">
-        <v>-26000</v>
+        <v>-1054000</v>
       </c>
       <c r="S8" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SMR 사업 관련 기대감에도 불구하고, 개인 투자자들은 시장 소외 및 정부 정책 부재에 대한 불만을 표출하며 주가 상승 동력 상실을 우려하고 있다.</t>
+          <t>주가 조작 의혹 및 불공정 거래 신고 관련 언급. 스페이스X 투자 기업으로서의 기대감과 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SMR', '개미', '외인']</t>
+          <t>['주가 조작', '스페이스X', '불공정거래']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7280</v>
+        <v>63900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="H9" t="n">
-        <v>25.45</v>
+        <v>22.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7270</v>
+        <v>62800</v>
       </c>
       <c r="K9" t="n">
-        <v>7360</v>
+        <v>63600</v>
       </c>
       <c r="L9" t="n">
-        <v>7420</v>
+        <v>64300</v>
       </c>
       <c r="M9" t="n">
-        <v>7250</v>
+        <v>62600</v>
       </c>
       <c r="N9" t="n">
-        <v>25.4</v>
+        <v>22.29</v>
       </c>
       <c r="O9" t="n">
-        <v>4433162365</v>
+        <v>36820345400</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>7190</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>39000</v>
+        <v>-26000</v>
       </c>
       <c r="S9" t="n">
-        <v>-5000</v>
+        <v>-23000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 비중 높은 종목이나 개인 매수세만으로는 상승력 부족. 업종 변경 및 주가 관리 부실 지적, 상폐 가능성 언급.</t>
+          <t>SMR 관련 기대감 속 주가 부진. 외인 매도 및 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 비중', '주가 관리', '개인 매수']</t>
+          <t>['SMR', '공매도', '주가 부진']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17260</v>
+        <v>7320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'+0.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="H10" t="n">
-        <v>27.78</v>
+        <v>25.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17320</v>
+        <v>7270</v>
       </c>
       <c r="K10" t="n">
-        <v>17480</v>
+        <v>7360</v>
       </c>
       <c r="L10" t="n">
-        <v>17820</v>
+        <v>7420</v>
       </c>
       <c r="M10" t="n">
-        <v>17170</v>
+        <v>7250</v>
       </c>
       <c r="N10" t="n">
-        <v>27.78</v>
+        <v>25.4</v>
       </c>
       <c r="O10" t="n">
-        <v>16053907045</v>
+        <v>4800549145</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>17170</v>
+        <v>7190</v>
       </c>
       <c r="R10" t="n">
-        <v>106000</v>
+        <v>39000</v>
       </c>
       <c r="S10" t="n">
-        <v>33000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조선업 섹터 부진 속 삼성중공업 주가 하락. 반도체 섹터로 자금 이동, 외인 매수세 유입에도 종목 자체 부진.</t>
+          <t>외인 비중 높은 종목이나 개인 매수세만으로는 상승력 부족. 업종 변경 및 주가 관리 부실 지적, 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선업', '주가 하락', '반도체 섹터']</t>
+          <t>['외인 비중', '주가 관리', '개인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3075</v>
+        <v>17430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.95%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3235</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>3170</v>
+        <v>17480</v>
       </c>
       <c r="L11" t="n">
-        <v>3200</v>
+        <v>17820</v>
       </c>
       <c r="M11" t="n">
-        <v>3035</v>
+        <v>17170</v>
       </c>
       <c r="N11" t="n">
-        <v>0.73</v>
+        <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>6380035922</v>
+        <v>17817013245</v>
       </c>
       <c r="P11" t="n">
-        <v>7050</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>2500</v>
+        <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>35000</v>
+        <v>106000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련주로 급락. 출처 불분명한 이슈에 따른 변동성 확대, 공매도 세력과의 갈등.</t>
+          <t>조선업황 부진 및 정치적 이슈 관련 부정적 전망. 반도체 섹터 이동 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '급락', '공매도']</t>
+          <t>['조선업', '주가 하락', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,97 +1476,189 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4265</v>
+        <v>3065</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'-5.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="H12" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4630</v>
+        <v>3235</v>
       </c>
       <c r="K12" t="n">
-        <v>4645</v>
+        <v>3170</v>
       </c>
       <c r="L12" t="n">
-        <v>4645</v>
+        <v>3200</v>
       </c>
       <c r="M12" t="n">
-        <v>4240</v>
+        <v>3035</v>
       </c>
       <c r="N12" t="n">
-        <v>8.57</v>
+        <v>0.73</v>
       </c>
       <c r="O12" t="n">
-        <v>14434286670</v>
+        <v>6642720122</v>
       </c>
       <c r="P12" t="n">
-        <v>7560</v>
+        <v>7050</v>
       </c>
       <c r="Q12" t="n">
-        <v>2930</v>
+        <v>2500</v>
       </c>
       <c r="R12" t="n">
-        <v>-638000</v>
+        <v>35000</v>
       </c>
       <c r="S12" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>프로그램 매도세 강하며 주가 하락 지속. 공매도 및 누르기 의혹 제기, 경영진 비판.</t>
+          <t>김정은 사망설 관련 변동성 확대. 공매도 관련 언급 및 주가 하락에 대한 불안감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['프로그램 매도', '공매도', '주가 누르기']</t>
+          <t>['김정은', '사망설', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4305</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-7.02%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38</v>
+      </c>
+      <c r="G13" t="n">
+        <v>279</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4630</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4645</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4645</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4240</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="O13" t="n">
+        <v>14917803076</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7560</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2930</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-638000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>주가 하락에 대한 불만 고조. 프로그램 매도 및 공매도 관련 부정적 언급 다수.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['공매도', '프로그램매도', '하락']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
         <v>1</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>088350</t>
         </is>

--- a/data/trending_integrated_20261021_10.xlsx
+++ b/data/trending_integrated_20261021_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10740</v>
+        <v>10750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+9.93%</t>
+          <t>'+10.03%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H2" t="n">
         <v>1.28</v>
@@ -610,7 +610,7 @@
         <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>119499549245</v>
+        <v>126892101015</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9340</v>
+        <v>9330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.98%</t>
+          <t>'+7.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="H3" t="n">
         <v>5.34</v>
@@ -693,7 +693,7 @@
         <v>9010</v>
       </c>
       <c r="L3" t="n">
-        <v>9380</v>
+        <v>9440</v>
       </c>
       <c r="M3" t="n">
         <v>8790</v>
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>10230097735</v>
+        <v>13248429465</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 철회 소식. 중복상장 금지 이슈와 테슬라 관련주로서의 기대감.</t>
+          <t>자회사 중복상장 금지 첫 적용 및 나스닥 상장 철회 확정. 호재로 작용.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['나스닥', '중복상장', '테슬라']</t>
+          <t>['중복상장', '상장철회', '테슬라']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1298000</v>
+        <v>1301000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.13%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G4" t="n">
-        <v>1374</v>
+        <v>1399</v>
       </c>
       <c r="H4" t="n">
         <v>48.77</v>
@@ -794,7 +794,7 @@
         <v>48.81</v>
       </c>
       <c r="O4" t="n">
-        <v>1935470610500</v>
+        <v>2036235627500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 이슈 및 V자 반등 기대감. 국내외 반도체 시장 상황 및 투자자 심리 관찰.</t>
+          <t>솔리다임 상장 이슈, 차트상 V자 반등 가능성 언급. 반도체 수출 회복 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['솔리다임', '반도체', 'V자 반등']</t>
+          <t>['반도체', '솔리다임', '수출']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>222250</v>
+        <v>223500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.08%</t>
+          <t>'+5.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="G5" t="n">
-        <v>1448</v>
+        <v>1429</v>
       </c>
       <c r="H5" t="n">
         <v>46.08</v>
@@ -886,7 +886,7 @@
         <v>46.04</v>
       </c>
       <c r="O5" t="n">
-        <v>1217249215500</v>
+        <v>1283648715250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국-중국 반도체 갈등 속 외국인 순매수 지속. 공매도 폐지 요구 및 반도체 판매 증가 추세.</t>
+          <t>미국 중국 반도체 퇴출 관련 뉴스, 외국인 3일간 순매수, 공매도 폐지 촉구. 조정 후 반등 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '공매도']</t>
+          <t>['반도체', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14540</v>
+        <v>14610</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.68%</t>
+          <t>'+3.18%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H6" t="n">
         <v>9.82</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>12781207500</v>
+        <v>13505964760</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 누르기 및 공매도 관련 불만 제기. 외국인, 연기금 매수세 유입 및 실적 개선 기대.</t>
+          <t>외국인, 연기금 매수에도 불구하고 종가 음봉 발생. 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '누르기', '실적주']</t>
+          <t>['실적주', '주가조작', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.93</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H7" t="n">
         <v>0.84</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>24406397273</v>
+        <v>24772478133</v>
       </c>
       <c r="P7" t="n">
         <v>2970</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>스페이스X 관련주 부각 및 주가 상승 기대. 다만, 개인 투자자 매수세와 프로그램 매도세 관찰 필요.</t>
+          <t>스페이스X 관련주로 언급되며 시간 외 급등 소식이 있으나, 매도 의견도 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['스페이스X', '수혜주', '강관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2900</v>
+        <v>2890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.11%</t>
+          <t>'+1.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="H8" t="n">
         <v>5.82</v>
@@ -1162,7 +1162,7 @@
         <v>5.91</v>
       </c>
       <c r="O8" t="n">
-        <v>14618787944</v>
+        <v>14815796034</v>
       </c>
       <c r="P8" t="n">
         <v>19950</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 불공정 거래 신고 관련 언급. 스페이스X 투자 기업으로서의 기대감과 단기 급등 가능성.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '스페이스X', '불공정거래']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.29</v>
       </c>
       <c r="O9" t="n">
-        <v>36820345400</v>
+        <v>39650744700</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SMR 관련 기대감 속 주가 부진. 외인 매도 및 공매도 관련 부정적 언급.</t>
+          <t>SMR, 태양광 등 언급에도 불구하고 지수 대비 낮은 상승률. 공매도 및 외인 매도 영향.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SMR', '공매도', '주가 부진']</t>
+          <t>['SMR', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7320</v>
+        <v>7340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.69%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H10" t="n">
         <v>25.45</v>
@@ -1346,7 +1346,7 @@
         <v>25.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4800549145</v>
+        <v>5059823485</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17430</v>
+        <v>17480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
         <v>141</v>
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>17817013245</v>
+        <v>18635502885</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,18 +1487,18 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3065</v>
+        <v>3085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.26%</t>
+          <t>'-4.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.73</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
         <v>26</v>
@@ -1530,7 +1530,7 @@
         <v>0.73</v>
       </c>
       <c r="O12" t="n">
-        <v>6642720122</v>
+        <v>6823859054</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4305</v>
+        <v>4315</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.02%</t>
+          <t>'-6.80%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="H13" t="n">
         <v>8.58</v>
@@ -1622,7 +1622,7 @@
         <v>8.57</v>
       </c>
       <c r="O13" t="n">
-        <v>14917803076</v>
+        <v>15206291125</v>
       </c>
       <c r="P13" t="n">
         <v>7560</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만 고조. 프로그램 매도 및 공매도 관련 부정적 언급 다수.</t>
+          <t>프로그램 매도세와 공매도로 인한 주가 하락에 대한 불만이 크며, 경영진 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램매도', '하락']</t>
+          <t>['공매도', '프로그램매도', '주가누르기']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1661,6 +1661,98 @@
       <c r="Z13" t="inlineStr">
         <is>
           <t>088350</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>푸드나무</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-19.74%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46</v>
+      </c>
+      <c r="F14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1480</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1115</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15638787818</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3980</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1115</v>
+      </c>
+      <c r="R14" t="n">
+        <v>606000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>하한가 기록, 자본 잠식 및 폐업 가능성 우려. 대주주 반대매매 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['자본잠식', '하한가', '반대매매']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>290720</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261021_10.xlsx
+++ b/data/trending_integrated_20261021_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>형지엘리트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10750</v>
+        <v>2435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+10.03%</t>
+          <t>'+26.56%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="H2" t="n">
-        <v>1.28</v>
+        <v>3.94</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9770</v>
+        <v>1924</v>
       </c>
       <c r="K2" t="n">
-        <v>10320</v>
+        <v>2310</v>
       </c>
       <c r="L2" t="n">
-        <v>11090</v>
+        <v>2500</v>
       </c>
       <c r="M2" t="n">
-        <v>9690</v>
+        <v>2200</v>
       </c>
       <c r="N2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>126892101015</v>
+        <v>8948396267</v>
       </c>
       <c r="P2" t="n">
-        <v>11250</v>
+        <v>2665</v>
       </c>
       <c r="Q2" t="n">
-        <v>2270</v>
+        <v>292</v>
       </c>
       <c r="R2" t="n">
-        <v>218000</v>
+        <v>-21000</v>
       </c>
       <c r="S2" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇주 섹터 상승 속 HT로보틱스 신고가 기대감. 고점 급락 우려와 함께 프로그램 매수세 관찰.</t>
+          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', '프로그램 매수']</t>
+          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>093240</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9330</v>
+        <v>11080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.86%</t>
+          <t>'+13.41%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.66</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>133</v>
+        <v>227</v>
       </c>
       <c r="H3" t="n">
-        <v>5.34</v>
+        <v>1.28</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8650</v>
+        <v>9770</v>
       </c>
       <c r="K3" t="n">
-        <v>9010</v>
+        <v>10320</v>
       </c>
       <c r="L3" t="n">
-        <v>9440</v>
+        <v>11160</v>
       </c>
       <c r="M3" t="n">
-        <v>8790</v>
+        <v>9690</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>0.88</v>
       </c>
       <c r="O3" t="n">
-        <v>13248429465</v>
+        <v>139132806825</v>
       </c>
       <c r="P3" t="n">
-        <v>14940</v>
+        <v>11250</v>
       </c>
       <c r="Q3" t="n">
-        <v>5390</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>-42000</v>
+        <v>218000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 중복상장 금지 첫 적용 및 나스닥 상장 철회 확정. 호재로 작용.</t>
+          <t>로봇주 섹터 상승 속 HT로보틱스 신고가 기대감. 고점 급락 우려와 함께 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['중복상장', '상장철회', '테슬라']</t>
+          <t>['로봇주', '신고가', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1301000</v>
+        <v>9220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.38%</t>
+          <t>'+6.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>511</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>1399</v>
+        <v>175</v>
       </c>
       <c r="H4" t="n">
-        <v>48.77</v>
+        <v>5.34</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1223000</v>
+        <v>8650</v>
       </c>
       <c r="K4" t="n">
-        <v>1260000</v>
+        <v>9010</v>
       </c>
       <c r="L4" t="n">
-        <v>1319000</v>
+        <v>9440</v>
       </c>
       <c r="M4" t="n">
-        <v>1258000</v>
+        <v>8790</v>
       </c>
       <c r="N4" t="n">
-        <v>48.81</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>2036235627500</v>
+        <v>14695969895</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q4" t="n">
-        <v>468000</v>
+        <v>5390</v>
       </c>
       <c r="R4" t="n">
-        <v>45000</v>
+        <v>-42000</v>
       </c>
       <c r="S4" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>솔리다임 상장 이슈, 차트상 V자 반등 가능성 언급. 반도체 수출 회복 기대.</t>
+          <t>자회사 나스닥 상장 철회(중복상장 금지 첫 적용)로 인한 호재. 테슬라 관련주로 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '솔리다임', '수출']</t>
+          <t>['중복상장 철회', '테슬라', '호재']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>223500</v>
+        <v>1302000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.67%</t>
+          <t>'+6.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="G5" t="n">
-        <v>1429</v>
+        <v>1445</v>
       </c>
       <c r="H5" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>211500</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>217000</v>
+        <v>1260000</v>
       </c>
       <c r="L5" t="n">
-        <v>224750</v>
+        <v>1319000</v>
       </c>
       <c r="M5" t="n">
-        <v>217000</v>
+        <v>1258000</v>
       </c>
       <c r="N5" t="n">
-        <v>46.04</v>
+        <v>48.81</v>
       </c>
       <c r="O5" t="n">
-        <v>1283648715250</v>
+        <v>2169271428000</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>446000</v>
+        <v>45000</v>
       </c>
       <c r="S5" t="n">
-        <v>262000</v>
+        <v>56000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 관련 뉴스, 외국인 3일간 순매수, 공매도 폐지 촉구. 조정 후 반등 기대.</t>
+          <t>솔리다임 상장 이슈와 반도체 업황 회복 기대감. 개인 매도와 외국인/개인 쌍끌이 매수에 대한 의견 분분.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '공매도', '외국인']</t>
+          <t>['솔리다임 상장', '반도체 수출', 'V자 반등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14610</v>
+        <v>224500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.18%</t>
+          <t>'+6.15%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>494</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>1414</v>
       </c>
       <c r="H6" t="n">
-        <v>9.82</v>
+        <v>46.08</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14160</v>
+        <v>211500</v>
       </c>
       <c r="K6" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="L6" t="n">
-        <v>14780</v>
+        <v>224750</v>
       </c>
       <c r="M6" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>13505964760</v>
+        <v>1370803001250</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>77000</v>
+        <v>446000</v>
       </c>
       <c r="S6" t="n">
-        <v>3000</v>
+        <v>262000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인, 연기금 매수에도 불구하고 종가 음봉 발생. 주가 누르기 의혹 제기.</t>
+          <t>외국인 대규모 순매수와 함께 반도체 관련 호재(미국 중국 반도체 퇴출 결정 등)로 인한 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적주', '주가조작', '공매도']</t>
+          <t>['외국인 순매수', '반도체', '공매도 폐지']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1616</v>
+        <v>14640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+3.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.93</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>9.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1573</v>
+        <v>14160</v>
       </c>
       <c r="K7" t="n">
-        <v>1650</v>
+        <v>14340</v>
       </c>
       <c r="L7" t="n">
-        <v>1715</v>
+        <v>14780</v>
       </c>
       <c r="M7" t="n">
-        <v>1573</v>
+        <v>14340</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>24772478133</v>
+        <v>14071272645</v>
       </c>
       <c r="P7" t="n">
-        <v>2970</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>890</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-553000</v>
+        <v>77000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>스페이스X 관련주로 언급되며 시간 외 급등 소식이 있으나, 매도 의견도 혼재.</t>
+          <t>정치적 이슈와 함께 실적주로서 외국인, 연기금 매수세 언급. 종가 음봉 및 기대감 하락.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '강관']</t>
+          <t>['실적주', '외국인 매수', '정치 이슈']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2890</v>
+        <v>1602</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.76%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09</v>
+        <v>-0.93</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="H8" t="n">
-        <v>5.82</v>
+        <v>0.84</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2840</v>
+        <v>1573</v>
       </c>
       <c r="K8" t="n">
-        <v>3100</v>
+        <v>1650</v>
       </c>
       <c r="L8" t="n">
-        <v>3300</v>
+        <v>1715</v>
       </c>
       <c r="M8" t="n">
-        <v>2855</v>
+        <v>1573</v>
       </c>
       <c r="N8" t="n">
-        <v>5.91</v>
+        <v>1.77</v>
       </c>
       <c r="O8" t="n">
-        <v>14815796034</v>
+        <v>25192536792</v>
       </c>
       <c r="P8" t="n">
-        <v>19950</v>
+        <v>2970</v>
       </c>
       <c r="Q8" t="n">
-        <v>1913</v>
+        <v>890</v>
       </c>
       <c r="R8" t="n">
-        <v>-1054000</v>
+        <v>-553000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>스페이스X 관련주로 부각되며 시간 외 폭등. 중동 종전, 알래스카 등 다양한 테마 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['스페이스X', '수혜주', '테마']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63900</v>
+        <v>2890</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+1.76%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="H9" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K9" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L9" t="n">
-        <v>64300</v>
+        <v>3300</v>
       </c>
       <c r="M9" t="n">
-        <v>62600</v>
+        <v>2855</v>
       </c>
       <c r="N9" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>39650744700</v>
+        <v>14907188924</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R9" t="n">
-        <v>-26000</v>
+        <v>-1054000</v>
       </c>
       <c r="S9" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SMR, 태양광 등 언급에도 불구하고 지수 대비 낮은 상승률. 공매도 및 외인 매도 영향.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SMR', '공매도', '외국인']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7340</v>
+        <v>63900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>176</v>
+        <v>337</v>
       </c>
       <c r="H10" t="n">
-        <v>25.45</v>
+        <v>22.23</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7270</v>
+        <v>62800</v>
       </c>
       <c r="K10" t="n">
-        <v>7360</v>
+        <v>63600</v>
       </c>
       <c r="L10" t="n">
-        <v>7420</v>
+        <v>64300</v>
       </c>
       <c r="M10" t="n">
-        <v>7250</v>
+        <v>62600</v>
       </c>
       <c r="N10" t="n">
-        <v>25.4</v>
+        <v>22.29</v>
       </c>
       <c r="O10" t="n">
-        <v>5059823485</v>
+        <v>41774674550</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>7190</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>39000</v>
+        <v>-26000</v>
       </c>
       <c r="S10" t="n">
-        <v>-5000</v>
+        <v>-23000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인 비중 높은 종목이나 개인 매수세만으로는 상승력 부족. 업종 변경 및 주가 관리 부실 지적, 상폐 가능성 언급.</t>
+          <t>SMR 관련 기대감과 공매도 이슈. 시장 소외 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인 비중', '주가 관리', '개인 매수']</t>
+          <t>['SMR', '공매도', '시장 소외']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17480</v>
+        <v>17600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>18635502885</v>
+        <v>19679528520</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선업황 부진 및 정치적 이슈 관련 부정적 전망. 반도체 섹터 이동 및 주가 하락 우려.</t>
+          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업', '주가 하락', '반도체']</t>
+          <t>['조선업', '실적 부진', '반도체 이동']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3085</v>
+        <v>7380</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.73</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3235</v>
+        <v>7270</v>
       </c>
       <c r="K12" t="n">
-        <v>3170</v>
+        <v>7360</v>
       </c>
       <c r="L12" t="n">
-        <v>3200</v>
+        <v>7420</v>
       </c>
       <c r="M12" t="n">
-        <v>3035</v>
+        <v>7250</v>
       </c>
       <c r="N12" t="n">
-        <v>0.73</v>
+        <v>25.4</v>
       </c>
       <c r="O12" t="n">
-        <v>6823859054</v>
+        <v>5434678285</v>
       </c>
       <c r="P12" t="n">
-        <v>7050</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>2500</v>
+        <v>7190</v>
       </c>
       <c r="R12" t="n">
-        <v>35000</v>
+        <v>39000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 변동성 확대. 공매도 관련 언급 및 주가 하락에 대한 불안감.</t>
+          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['김정은', '사망설', '공매도']</t>
+          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4315</v>
+        <v>3065</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-6.80%</t>
+          <t>'-5.26%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>288</v>
+        <v>131</v>
       </c>
       <c r="H13" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4630</v>
+        <v>3235</v>
       </c>
       <c r="K13" t="n">
-        <v>4645</v>
+        <v>3170</v>
       </c>
       <c r="L13" t="n">
-        <v>4645</v>
+        <v>3200</v>
       </c>
       <c r="M13" t="n">
-        <v>4240</v>
+        <v>3035</v>
       </c>
       <c r="N13" t="n">
-        <v>8.57</v>
+        <v>0.73</v>
       </c>
       <c r="O13" t="n">
-        <v>15206291125</v>
+        <v>7102250989</v>
       </c>
       <c r="P13" t="n">
-        <v>7560</v>
+        <v>7050</v>
       </c>
       <c r="Q13" t="n">
-        <v>2930</v>
+        <v>2500</v>
       </c>
       <c r="R13" t="n">
-        <v>-638000</v>
+        <v>35000</v>
       </c>
       <c r="S13" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>프로그램 매도세와 공매도로 인한 주가 하락에 대한 불만이 크며, 경영진 비판.</t>
+          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램매도', '주가누르기']</t>
+          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>088350</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1220</v>
+        <v>4325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-19.74%</t>
+          <t>'-6.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>39</v>
+        <v>300</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1520</v>
+        <v>4630</v>
       </c>
       <c r="K14" t="n">
-        <v>1132</v>
+        <v>4645</v>
       </c>
       <c r="L14" t="n">
-        <v>1480</v>
+        <v>4645</v>
       </c>
       <c r="M14" t="n">
-        <v>1115</v>
+        <v>4240</v>
       </c>
       <c r="N14" t="n">
-        <v>0.57</v>
+        <v>8.57</v>
       </c>
       <c r="O14" t="n">
-        <v>15638787818</v>
+        <v>15741204993</v>
       </c>
       <c r="P14" t="n">
-        <v>3980</v>
+        <v>7560</v>
       </c>
       <c r="Q14" t="n">
-        <v>1115</v>
+        <v>2930</v>
       </c>
       <c r="R14" t="n">
-        <v>606000</v>
+        <v>-638000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>하한가 기록, 자본 잠식 및 폐업 가능성 우려. 대주주 반대매매 가능성 언급.</t>
+          <t>프로그램 매도세와 공매도로 인한 주가 하락에 대한 불만이 크며, 경영진 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자본잠식', '하한가', '반대매매']</t>
+          <t>['공매도', '프로그램매도', '주가누르기']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1751,6 +1751,98 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>088350</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>푸드나무</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1213</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-20.20%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>47</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1115</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15847710391</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3980</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1115</v>
+      </c>
+      <c r="R15" t="n">
+        <v>606000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>자본 잠식 및 부도/폐업 가능성 언급. 대주주 반대매매, 횡령, 상폐 우려.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['자본 잠식', '부도', '상폐 우려']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>290720</t>
         </is>

--- a/data/trending_integrated_20261021_10.xlsx
+++ b/data/trending_integrated_20261021_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2435</v>
+        <v>2410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+26.56%</t>
+          <t>'+25.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>8948396267</v>
+        <v>9219940404</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11080</v>
+        <v>14825</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.41%</t>
+          <t>'+22.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>227</v>
+        <v>54</v>
       </c>
       <c r="H3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9770</v>
+        <v>12080</v>
       </c>
       <c r="K3" t="n">
-        <v>10320</v>
+        <v>12280</v>
       </c>
       <c r="L3" t="n">
-        <v>11160</v>
+        <v>15640</v>
       </c>
       <c r="M3" t="n">
-        <v>9690</v>
+        <v>12280</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>139132806825</v>
+        <v>80108133905</v>
       </c>
       <c r="P3" t="n">
-        <v>11250</v>
+        <v>28800</v>
       </c>
       <c r="Q3" t="n">
-        <v>2270</v>
+        <v>12030</v>
       </c>
       <c r="R3" t="n">
-        <v>218000</v>
+        <v>119000</v>
       </c>
       <c r="S3" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇주 섹터 상승 속 HT로보틱스 신고가 기대감. 고점 급락 우려와 함께 프로그램 매수세 관찰.</t>
+          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', '프로그램 매수']</t>
+          <t>['노광 장비', '엘리스', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9220</v>
+        <v>11610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.59%</t>
+          <t>'+18.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.66</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="H4" t="n">
-        <v>5.34</v>
+        <v>1.28</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8650</v>
+        <v>9770</v>
       </c>
       <c r="K4" t="n">
-        <v>9010</v>
+        <v>10320</v>
       </c>
       <c r="L4" t="n">
-        <v>9440</v>
+        <v>11690</v>
       </c>
       <c r="M4" t="n">
-        <v>8790</v>
+        <v>9690</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>14695969895</v>
+        <v>168824455100</v>
       </c>
       <c r="P4" t="n">
-        <v>14940</v>
+        <v>11690</v>
       </c>
       <c r="Q4" t="n">
-        <v>5390</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>-42000</v>
+        <v>218000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 철회(중복상장 금지 첫 적용)로 인한 호재. 테슬라 관련주로 언급.</t>
+          <t>로봇주 섹터 상승 속 신고가 경신. 개인 매물 소화 후 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['중복상장 철회', '테슬라', '호재']</t>
+          <t>['로봇주', '신고가', '매물 소화']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1302000</v>
+        <v>1318000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.46%</t>
+          <t>'+7.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G5" t="n">
-        <v>1445</v>
+        <v>1462</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.81</v>
       </c>
       <c r="O5" t="n">
-        <v>2169271428000</v>
+        <v>2333920385500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 이슈와 반도체 업황 회복 기대감. 개인 매도와 외국인/개인 쌍끌이 매수에 대한 의견 분분.</t>
+          <t>외국인, 기관 순매수 진입으로 인한 V자 반등 기대. 반도체 수출 회복 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임 상장', '반도체 수출', 'V자 반등']</t>
+          <t>['외국인', '기관', '반도체']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>224500</v>
+        <v>227000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.15%</t>
+          <t>'+7.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G6" t="n">
-        <v>1414</v>
+        <v>1714</v>
       </c>
       <c r="H6" t="n">
         <v>46.08</v>
@@ -969,7 +969,7 @@
         <v>217000</v>
       </c>
       <c r="L6" t="n">
-        <v>224750</v>
+        <v>227500</v>
       </c>
       <c r="M6" t="n">
         <v>217000</v>
@@ -978,7 +978,7 @@
         <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>1370803001250</v>
+        <v>1548810412500</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 대규모 순매수와 함께 반도체 관련 호재(미국 중국 반도체 퇴출 결정 등)로 인한 상승 기대.</t>
+          <t>외국인 대규모 순매수 유입에 따른 반도체 섹터 상승 기대. 공매도 폐지 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '반도체', '공매도 폐지']</t>
+          <t>['외국인', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14640</v>
+        <v>9220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.39%</t>
+          <t>'+6.59%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="H7" t="n">
-        <v>9.82</v>
+        <v>5.34</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14160</v>
+        <v>8650</v>
       </c>
       <c r="K7" t="n">
-        <v>14340</v>
+        <v>9010</v>
       </c>
       <c r="L7" t="n">
-        <v>14780</v>
+        <v>9440</v>
       </c>
       <c r="M7" t="n">
-        <v>14340</v>
+        <v>8790</v>
       </c>
       <c r="N7" t="n">
-        <v>9.779999999999999</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>14071272645</v>
+        <v>15531451030</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>14940</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>5390</v>
       </c>
       <c r="R7" t="n">
-        <v>77000</v>
+        <v>-42000</v>
       </c>
       <c r="S7" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 실적주로서 외국인, 연기금 매수세 언급. 종가 음봉 및 기대감 하락.</t>
+          <t>자회사 나스닥 상장 철회로 인한 중복 상장 금지 첫 적용. 테슬라 관련주.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적주', '외국인 매수', '정치 이슈']</t>
+          <t>['테슬라', '중복상장', '나스닥']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1602</v>
+        <v>14710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.93</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H8" t="n">
-        <v>0.84</v>
+        <v>9.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1573</v>
+        <v>14160</v>
       </c>
       <c r="K8" t="n">
-        <v>1650</v>
+        <v>14340</v>
       </c>
       <c r="L8" t="n">
-        <v>1715</v>
+        <v>14780</v>
       </c>
       <c r="M8" t="n">
-        <v>1573</v>
+        <v>14340</v>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>25192536792</v>
+        <v>14787114595</v>
       </c>
       <c r="P8" t="n">
-        <v>2970</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>890</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-553000</v>
+        <v>77000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>스페이스X 관련주로 부각되며 시간 외 폭등. 중동 종전, 알래스카 등 다양한 테마 언급.</t>
+          <t>주가 하락 및 윗꼬리 음봉 형성. 공매도 집중 및 실적 기대감 부재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '테마']</t>
+          <t>['주가 하락', '공매도', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2890</v>
+        <v>1619</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.76%</t>
+          <t>'+2.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>-0.93</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>5.82</v>
+        <v>0.84</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2840</v>
+        <v>1573</v>
       </c>
       <c r="K9" t="n">
-        <v>3100</v>
+        <v>1650</v>
       </c>
       <c r="L9" t="n">
-        <v>3300</v>
+        <v>1715</v>
       </c>
       <c r="M9" t="n">
-        <v>2855</v>
+        <v>1573</v>
       </c>
       <c r="N9" t="n">
-        <v>5.91</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>14907188924</v>
+        <v>26090939434</v>
       </c>
       <c r="P9" t="n">
-        <v>19950</v>
+        <v>2970</v>
       </c>
       <c r="Q9" t="n">
-        <v>1913</v>
+        <v>890</v>
       </c>
       <c r="R9" t="n">
-        <v>-1054000</v>
+        <v>-553000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63900</v>
+        <v>2920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="H10" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K10" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L10" t="n">
-        <v>64300</v>
+        <v>3300</v>
       </c>
       <c r="M10" t="n">
-        <v>62600</v>
+        <v>2855</v>
       </c>
       <c r="N10" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O10" t="n">
-        <v>41774674550</v>
+        <v>15187590085</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R10" t="n">
-        <v>-26000</v>
+        <v>-1054000</v>
       </c>
       <c r="S10" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SMR 관련 기대감과 공매도 이슈. 시장 소외 및 정부 정책 비판.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SMR', '공매도', '시장 소외']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17600</v>
+        <v>64400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.62%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>147</v>
+        <v>348</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>22.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17320</v>
+        <v>62800</v>
       </c>
       <c r="K11" t="n">
-        <v>17480</v>
+        <v>63600</v>
       </c>
       <c r="L11" t="n">
-        <v>17820</v>
+        <v>64500</v>
       </c>
       <c r="M11" t="n">
-        <v>17170</v>
+        <v>62600</v>
       </c>
       <c r="N11" t="n">
-        <v>27.78</v>
+        <v>22.29</v>
       </c>
       <c r="O11" t="n">
-        <v>19679528520</v>
+        <v>45691929400</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>17170</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>106000</v>
+        <v>-26000</v>
       </c>
       <c r="S11" t="n">
-        <v>33000</v>
+        <v>-23000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
+          <t>SMR 관련 기대감과 공매도 이슈. 시장 소외 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업', '실적 부진', '반도체 이동']</t>
+          <t>['SMR', '공매도', '시장 소외']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7380</v>
+        <v>17660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+1.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="H12" t="n">
-        <v>25.45</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7270</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>7360</v>
+        <v>17480</v>
       </c>
       <c r="L12" t="n">
-        <v>7420</v>
+        <v>17820</v>
       </c>
       <c r="M12" t="n">
-        <v>7250</v>
+        <v>17170</v>
       </c>
       <c r="N12" t="n">
-        <v>25.4</v>
+        <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>5434678285</v>
+        <v>20856791510</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>7190</v>
+        <v>17170</v>
       </c>
       <c r="R12" t="n">
-        <v>39000</v>
+        <v>106000</v>
       </c>
       <c r="S12" t="n">
-        <v>-5000</v>
+        <v>33000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
+          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
+          <t>['조선업', '실적 부진', '반도체 이동']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3065</v>
+        <v>7410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.26%</t>
+          <t>'+1.93%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.73</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3235</v>
+        <v>7270</v>
       </c>
       <c r="K13" t="n">
-        <v>3170</v>
+        <v>7360</v>
       </c>
       <c r="L13" t="n">
-        <v>3200</v>
+        <v>7420</v>
       </c>
       <c r="M13" t="n">
-        <v>3035</v>
+        <v>7250</v>
       </c>
       <c r="N13" t="n">
-        <v>0.73</v>
+        <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>7102250989</v>
+        <v>6223745235</v>
       </c>
       <c r="P13" t="n">
-        <v>7050</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>2500</v>
+        <v>7190</v>
       </c>
       <c r="R13" t="n">
-        <v>35000</v>
+        <v>39000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
+          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
+          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4325</v>
+        <v>3060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.59%</t>
+          <t>'-5.41%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>300</v>
+        <v>135</v>
       </c>
       <c r="H14" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4630</v>
+        <v>3235</v>
       </c>
       <c r="K14" t="n">
-        <v>4645</v>
+        <v>3170</v>
       </c>
       <c r="L14" t="n">
-        <v>4645</v>
+        <v>3200</v>
       </c>
       <c r="M14" t="n">
-        <v>4240</v>
+        <v>3035</v>
       </c>
       <c r="N14" t="n">
-        <v>8.57</v>
+        <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>15741204993</v>
+        <v>7353339729</v>
       </c>
       <c r="P14" t="n">
-        <v>7560</v>
+        <v>7050</v>
       </c>
       <c r="Q14" t="n">
-        <v>2930</v>
+        <v>2500</v>
       </c>
       <c r="R14" t="n">
-        <v>-638000</v>
+        <v>35000</v>
       </c>
       <c r="S14" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>프로그램 매도세와 공매도로 인한 주가 하락에 대한 불만이 크며, 경영진 비판.</t>
+          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램매도', '주가누르기']</t>
+          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>088350</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1213</v>
+        <v>4305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-20.20%</t>
+          <t>'-7.02%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>46</v>
+        <v>306</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1520</v>
+        <v>4630</v>
       </c>
       <c r="K15" t="n">
-        <v>1132</v>
+        <v>4645</v>
       </c>
       <c r="L15" t="n">
-        <v>1480</v>
+        <v>4645</v>
       </c>
       <c r="M15" t="n">
-        <v>1115</v>
+        <v>4240</v>
       </c>
       <c r="N15" t="n">
-        <v>0.57</v>
+        <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>15847710391</v>
+        <v>16063210853</v>
       </c>
       <c r="P15" t="n">
-        <v>3980</v>
+        <v>7560</v>
       </c>
       <c r="Q15" t="n">
-        <v>1115</v>
+        <v>2930</v>
       </c>
       <c r="R15" t="n">
-        <v>606000</v>
+        <v>-638000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자본 잠식 및 부도/폐업 가능성 언급. 대주주 반대매매, 횡령, 상폐 우려.</t>
+          <t>프로그램 매도 및 공매도 집중으로 인한 주가 하락. 경영진 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자본 잠식', '부도', '상폐 우려']</t>
+          <t>['공매도', '프로그램매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1843,6 +1843,98 @@
         </is>
       </c>
       <c r="Z15" t="inlineStr">
+        <is>
+          <t>088350</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>푸드나무</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1217</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-19.93%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37</v>
+      </c>
+      <c r="G16" t="n">
+        <v>53</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1480</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1115</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O16" t="n">
+        <v>16095715892</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3980</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1115</v>
+      </c>
+      <c r="R16" t="n">
+        <v>606000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>하한가 기록 후 추가 하락 우려. 자본 잠식 및 부도설 제기.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['하한가', '자본 잠식', '부도']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>290720</t>
         </is>
